--- a/data/trans_dic/P1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 10,93</t>
+          <t>5,62; 10,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,5</t>
+          <t>8,36; 14,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,6; 26,7</t>
+          <t>17,14; 25,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 21,42</t>
+          <t>14,07; 21,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 13,02</t>
+          <t>6,35; 12,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 17,38</t>
+          <t>9,14; 17,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,4</t>
+          <t>10,35; 18,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,91; 19,59</t>
+          <t>13,62; 19,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,73</t>
+          <t>6,47; 10,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,49; 14,57</t>
+          <t>9,8; 14,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 21,55</t>
+          <t>15,58; 21,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,37</t>
+          <t>14,66; 19,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 16,34</t>
+          <t>9,13; 16,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,45</t>
+          <t>6,21; 12,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 13,78</t>
+          <t>7,33; 13,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,39; 22,4</t>
+          <t>15,06; 22,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,39</t>
+          <t>4,88; 10,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 11,04</t>
+          <t>5,08; 11,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,37</t>
+          <t>9,42; 16,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 17,03</t>
+          <t>11,61; 16,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,43</t>
+          <t>7,67; 12,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,91</t>
+          <t>6,3; 10,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,04</t>
+          <t>9,07; 13,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,98; 18,79</t>
+          <t>14,27; 18,84</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,02</t>
+          <t>3,88; 7,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,74</t>
+          <t>5,65; 10,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 13,54</t>
+          <t>8,41; 13,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 19,99</t>
+          <t>4,29; 19,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,55</t>
+          <t>3,33; 10,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,74</t>
+          <t>7,76; 15,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 23,82</t>
+          <t>11,24; 23,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 26,58</t>
+          <t>16,44; 26,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,81</t>
+          <t>4,19; 7,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 11,32</t>
+          <t>7,21; 11,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,03</t>
+          <t>9,92; 15,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 20,46</t>
+          <t>6,75; 20,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,2</t>
+          <t>5,29; 8,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,66</t>
+          <t>7,12; 10,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,42</t>
+          <t>8,85; 12,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,76; 21,68</t>
+          <t>16,85; 21,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,24</t>
+          <t>5,45; 9,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,39</t>
+          <t>3,76; 7,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 15,43</t>
+          <t>10,43; 15,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 15,51</t>
+          <t>6,44; 15,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,08</t>
+          <t>5,76; 8,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,72</t>
+          <t>6,19; 8,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 13,01</t>
+          <t>10,02; 12,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 17,8</t>
+          <t>10,43; 17,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,83</t>
+          <t>6,91; 13,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,49</t>
+          <t>5,77; 10,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,2; 18,11</t>
+          <t>12,07; 17,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,13; 26,9</t>
+          <t>18,82; 26,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 10,75</t>
+          <t>6,09; 11,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,73</t>
+          <t>8,36; 12,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,15; 14,11</t>
+          <t>9,18; 14,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,64</t>
+          <t>13,58; 21,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,1</t>
+          <t>7,34; 11,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,24</t>
+          <t>7,91; 11,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 15,04</t>
+          <t>11,46; 14,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,4; 22,5</t>
+          <t>16,44; 22,75</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,67</t>
+          <t>0,94; 5,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,4</t>
+          <t>1,21; 5,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,6; 12,39</t>
+          <t>5,37; 12,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 15,91</t>
+          <t>1,95; 13,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,4</t>
+          <t>8,71; 12,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,42; 14,45</t>
+          <t>10,37; 14,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,56</t>
+          <t>11,81; 16,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,96; 22,96</t>
+          <t>18,33; 23,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,35</t>
+          <t>7,45; 10,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,3</t>
+          <t>8,78; 12,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,01</t>
+          <t>10,79; 14,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,31</t>
+          <t>14,68; 19,36</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 8,28</t>
+          <t>6,39; 8,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,43</t>
+          <t>7,34; 9,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,35; 13,7</t>
+          <t>11,41; 13,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,11; 18,75</t>
+          <t>13,45; 18,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 9,81</t>
+          <t>7,81; 9,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 10,99</t>
+          <t>8,97; 11,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,13; 14,62</t>
+          <t>12,01; 14,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,49; 17,99</t>
+          <t>13,48; 18,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 8,69</t>
+          <t>7,37; 8,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,49; 9,88</t>
+          <t>8,47; 9,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,08; 13,76</t>
+          <t>12,08; 13,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,52; 18,04</t>
+          <t>14,42; 17,93</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26280; 51794</t>
+          <t>26604; 51116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36207; 63398</t>
+          <t>36534; 64176</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75526; 114566</t>
+          <t>73531; 111100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71299; 108194</t>
+          <t>71107; 107439</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20055; 39940</t>
+          <t>19481; 39057</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29039; 54663</t>
+          <t>28736; 56043</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35998; 63870</t>
+          <t>35926; 64579</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62257; 87664</t>
+          <t>60966; 87575</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52363; 83705</t>
+          <t>50494; 83350</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71302; 109485</t>
+          <t>73660; 110914</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120595; 167227</t>
+          <t>120931; 165386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>141298; 184581</t>
+          <t>139628; 182677</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33074; 59972</t>
+          <t>33508; 61977</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26178; 52148</t>
+          <t>26013; 50461</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27705; 51985</t>
+          <t>27636; 50456</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69617; 101285</t>
+          <t>68099; 100638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18526; 38650</t>
+          <t>18152; 37170</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16827; 37323</t>
+          <t>17184; 37926</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34001; 60939</t>
+          <t>35076; 62128</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43373; 65161</t>
+          <t>44435; 64945</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58106; 91801</t>
+          <t>56631; 91698</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48832; 82535</t>
+          <t>47708; 79974</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68615; 105258</t>
+          <t>68013; 103115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>116739; 156830</t>
+          <t>119129; 157293</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20868; 43507</t>
+          <t>21050; 43255</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36802; 67593</t>
+          <t>35563; 66266</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42553; 70691</t>
+          <t>43898; 72417</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29091; 133619</t>
+          <t>28650; 133125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6067; 19376</t>
+          <t>5583; 18316</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19755; 40956</t>
+          <t>20191; 40101</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17644; 39569</t>
+          <t>18670; 39004</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27845; 44368</t>
+          <t>27436; 43864</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29992; 55494</t>
+          <t>29784; 54998</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63350; 100683</t>
+          <t>64130; 99451</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66335; 103407</t>
+          <t>68256; 103934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48922; 170875</t>
+          <t>56380; 169135</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66953; 101498</t>
+          <t>65460; 102889</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83486; 123568</t>
+          <t>82470; 121231</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99966; 142829</t>
+          <t>101777; 141597</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173430; 224375</t>
+          <t>174391; 224821</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39006; 65970</t>
+          <t>38917; 67790</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29642; 56675</t>
+          <t>28862; 55966</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87320; 127427</t>
+          <t>86162; 129607</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57531; 151670</t>
+          <t>62987; 150539</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>113354; 157711</t>
+          <t>112494; 157795</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>121551; 167993</t>
+          <t>119278; 164884</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200837; 257111</t>
+          <t>198008; 256193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>217435; 358331</t>
+          <t>209961; 356895</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>25462; 48487</t>
+          <t>24234; 48460</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28726; 53542</t>
+          <t>29482; 54149</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75735; 112404</t>
+          <t>74911; 110627</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90867; 127783</t>
+          <t>89425; 128035</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35736; 61121</t>
+          <t>34650; 62904</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63222; 96932</t>
+          <t>63648; 98767</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67586; 104149</t>
+          <t>67754; 103864</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117543; 182060</t>
+          <t>114293; 182535</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67007; 102024</t>
+          <t>67469; 103040</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99851; 143045</t>
+          <t>100639; 142142</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154734; 204416</t>
+          <t>155692; 200904</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>215918; 296220</t>
+          <t>216463; 299462</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2724; 13927</t>
+          <t>2801; 14903</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3189; 14409</t>
+          <t>3218; 14203</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16088; 35582</t>
+          <t>15406; 35229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4749; 38262</t>
+          <t>4696; 32815</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>110370; 154796</t>
+          <t>108818; 153903</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>115625; 160299</t>
+          <t>115086; 160369</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>128147; 179164</t>
+          <t>127821; 175600</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>136756; 174833</t>
+          <t>139549; 176816</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>114216; 160141</t>
+          <t>115326; 162287</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>122245; 169231</t>
+          <t>120804; 170600</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>152484; 205464</t>
+          <t>147760; 203872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>147827; 193434</t>
+          <t>147078; 193958</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>209937; 270930</t>
+          <t>208894; 270457</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>249558; 322603</t>
+          <t>251247; 320672</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>384169; 463953</t>
+          <t>386193; 463663</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>442701; 633167</t>
+          <t>454229; 635500</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>266389; 331430</t>
+          <t>263915; 333247</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>316939; 390171</t>
+          <t>318557; 391109</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>428406; 516185</t>
+          <t>424266; 513675</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>482538; 643790</t>
+          <t>482380; 649175</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>491032; 578056</t>
+          <t>490279; 579501</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>591893; 688869</t>
+          <t>590588; 690751</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>835690; 951913</t>
+          <t>835327; 953403</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1009593; 1254433</t>
+          <t>1002690; 1246614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,79</t>
+          <t>5,78; 10,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 14,68</t>
+          <t>8,42; 14,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,14; 25,89</t>
+          <t>17,28; 25,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 21,27</t>
+          <t>14,16; 21,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 12,74</t>
+          <t>6,59; 13,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,14; 17,82</t>
+          <t>9,34; 17,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 18,61</t>
+          <t>10,91; 18,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,62; 19,57</t>
+          <t>14,34; 19,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,68</t>
+          <t>6,5; 10,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,76</t>
+          <t>9,6; 14,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,31</t>
+          <t>15,55; 21,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,66; 19,18</t>
+          <t>15,06; 19,61</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,89</t>
+          <t>8,93; 16,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 12,05</t>
+          <t>6,18; 12,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 13,38</t>
+          <t>7,17; 13,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,06; 22,25</t>
+          <t>15,02; 22,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,0</t>
+          <t>5,23; 10,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 11,22</t>
+          <t>5,18; 11,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 16,69</t>
+          <t>9,29; 16,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,61; 16,98</t>
+          <t>11,77; 17,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,41</t>
+          <t>7,84; 12,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,57</t>
+          <t>6,54; 10,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,76</t>
+          <t>9,23; 14,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,27; 18,84</t>
+          <t>14,43; 18,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,97</t>
+          <t>3,83; 8,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,53</t>
+          <t>5,91; 10,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,88</t>
+          <t>8,15; 13,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 19,92</t>
+          <t>14,66; 21,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,92</t>
+          <t>3,41; 10,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 15,42</t>
+          <t>7,62; 15,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 23,48</t>
+          <t>11,03; 23,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,44; 26,28</t>
+          <t>16,33; 25,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,74</t>
+          <t>4,23; 7,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,18</t>
+          <t>7,2; 11,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 15,11</t>
+          <t>9,96; 15,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 20,25</t>
+          <t>16,19; 21,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,31</t>
+          <t>5,28; 8,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,46</t>
+          <t>7,17; 10,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,32</t>
+          <t>8,77; 12,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 21,73</t>
+          <t>16,89; 21,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 9,49</t>
+          <t>5,32; 9,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,3</t>
+          <t>3,92; 7,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,69</t>
+          <t>10,72; 15,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 15,39</t>
+          <t>12,56; 16,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,08</t>
+          <t>5,75; 8,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,56</t>
+          <t>6,25; 8,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 12,97</t>
+          <t>10,05; 12,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 17,73</t>
+          <t>15,7; 19,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,82</t>
+          <t>7,0; 13,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,61</t>
+          <t>5,82; 10,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,07; 17,82</t>
+          <t>12,29; 18,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,82; 26,95</t>
+          <t>20,68; 28,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,06</t>
+          <t>6,2; 11,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 12,97</t>
+          <t>8,59; 13,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 14,07</t>
+          <t>9,21; 14,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 21,7</t>
+          <t>18,24; 22,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,21</t>
+          <t>7,21; 10,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,17</t>
+          <t>7,87; 11,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,46; 14,78</t>
+          <t>11,35; 15,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,44; 22,75</t>
+          <t>20,03; 24,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,0</t>
+          <t>0,93; 4,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,32</t>
+          <t>1,25; 5,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 12,27</t>
+          <t>5,53; 12,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 13,64</t>
+          <t>1,91; 9,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,32</t>
+          <t>8,92; 12,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,46</t>
+          <t>10,49; 14,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,81; 16,23</t>
+          <t>11,98; 16,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,33; 23,22</t>
+          <t>17,92; 22,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,49</t>
+          <t>7,63; 10,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,4</t>
+          <t>8,87; 12,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 14,89</t>
+          <t>11,17; 15,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,68; 19,36</t>
+          <t>14,66; 18,66</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,27</t>
+          <t>6,36; 8,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 9,37</t>
+          <t>7,33; 9,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,41; 13,69</t>
+          <t>11,35; 13,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,82</t>
+          <t>17,3; 20,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,81; 9,86</t>
+          <t>7,86; 9,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,97; 11,02</t>
+          <t>8,9; 10,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,01; 14,55</t>
+          <t>12,22; 14,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,48; 18,14</t>
+          <t>16,61; 18,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,37; 8,72</t>
+          <t>7,46; 8,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,47; 9,91</t>
+          <t>8,48; 10,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,08; 13,78</t>
+          <t>12,06; 13,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 17,93</t>
+          <t>17,2; 18,94</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87436</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>83202</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>161689</t>
+          <t>178174</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26604; 51116</t>
+          <t>27367; 52049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36534; 64176</t>
+          <t>36815; 64419</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73531; 111100</t>
+          <t>74127; 111409</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71107; 107439</t>
+          <t>77994; 115780</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19481; 39057</t>
+          <t>20197; 40032</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28736; 56043</t>
+          <t>29369; 55917</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35926; 64579</t>
+          <t>37857; 65423</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>60966; 87575</t>
+          <t>70054; 96738</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50494; 83350</t>
+          <t>50721; 83040</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73660; 110914</t>
+          <t>72161; 110063</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120931; 165386</t>
+          <t>120701; 167011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>139628; 182677</t>
+          <t>156520; 203780</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>88795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54010</t>
+          <t>60980</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>137817</t>
+          <t>149775</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33508; 61977</t>
+          <t>32767; 59217</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26013; 50461</t>
+          <t>25870; 51269</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27636; 50456</t>
+          <t>27053; 50532</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68099; 100638</t>
+          <t>72564; 107455</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18152; 37170</t>
+          <t>19438; 39066</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17184; 37926</t>
+          <t>17524; 37396</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35076; 62128</t>
+          <t>34598; 62519</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44435; 64945</t>
+          <t>49785; 73931</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56631; 91698</t>
+          <t>57907; 92267</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47708; 79974</t>
+          <t>49523; 81617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68013; 103115</t>
+          <t>69146; 105549</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>119129; 157293</t>
+          <t>130798; 172110</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80180</t>
+          <t>85167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35211</t>
+          <t>38932</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>115391</t>
+          <t>124099</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21050; 43255</t>
+          <t>20751; 43860</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35563; 66266</t>
+          <t>37176; 68774</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43898; 72417</t>
+          <t>42526; 70691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28650; 133125</t>
+          <t>69158; 103277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5583; 18316</t>
+          <t>5713; 18214</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20191; 40101</t>
+          <t>19814; 39622</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18670; 39004</t>
+          <t>18318; 38970</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27436; 43864</t>
+          <t>30624; 48008</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29784; 54998</t>
+          <t>30070; 55059</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64130; 99451</t>
+          <t>64079; 99127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68256; 103934</t>
+          <t>68518; 103635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56380; 169135</t>
+          <t>106710; 144494</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197587</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>112952</t>
+          <t>123241</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>310539</t>
+          <t>343266</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65460; 102889</t>
+          <t>65436; 102701</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82470; 121231</t>
+          <t>83143; 124966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>101777; 141597</t>
+          <t>100877; 143580</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174391; 224821</t>
+          <t>191215; 248387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38917; 67790</t>
+          <t>38015; 65605</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28862; 55966</t>
+          <t>30051; 56121</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86162; 129607</t>
+          <t>88520; 128306</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>62987; 150539</t>
+          <t>108182; 142696</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112494; 157795</t>
+          <t>112335; 157132</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>119278; 164884</t>
+          <t>120285; 166937</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>198008; 256193</t>
+          <t>198484; 256389</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>209961; 356895</t>
+          <t>312921; 380290</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>140943</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>157191</t>
+          <t>168407</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>265811</t>
+          <t>309350</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24234; 48460</t>
+          <t>24525; 48761</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>29482; 54149</t>
+          <t>29726; 55036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74911; 110627</t>
+          <t>76283; 112194</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89425; 128035</t>
+          <t>117448; 162928</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34650; 62904</t>
+          <t>35282; 63290</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>63648; 98767</t>
+          <t>65436; 99886</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67754; 103864</t>
+          <t>68029; 104418</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>114293; 182535</t>
+          <t>151584; 185868</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67469; 103040</t>
+          <t>66245; 100342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100639; 142142</t>
+          <t>100144; 144493</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155692; 200904</t>
+          <t>154287; 204163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>216463; 299462</t>
+          <t>280198; 338614</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>156432</t>
+          <t>169062</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>168397</t>
+          <t>179346</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2801; 14903</t>
+          <t>2783; 14304</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3218; 14203</t>
+          <t>3346; 14207</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15406; 35229</t>
+          <t>15876; 34886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4696; 32815</t>
+          <t>4527; 21641</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>108818; 153903</t>
+          <t>111444; 156821</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>115086; 160369</t>
+          <t>116394; 159287</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>127821; 175600</t>
+          <t>129674; 178953</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>139549; 176816</t>
+          <t>151269; 189822</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>115326; 162287</t>
+          <t>118019; 163686</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>120804; 170600</t>
+          <t>122139; 169369</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>147760; 203872</t>
+          <t>152917; 205629</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>147078; 193958</t>
+          <t>158594; 201777</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>569593</t>
+          <t>640187</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>590050</t>
+          <t>643823</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1159643</t>
+          <t>1284010</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>208894; 270457</t>
+          <t>207856; 269765</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>251247; 320672</t>
+          <t>250759; 320468</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>386193; 463663</t>
+          <t>384427; 461398</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>454229; 635500</t>
+          <t>595586; 690721</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>263915; 333247</t>
+          <t>265543; 329610</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>318557; 391109</t>
+          <t>315812; 390000</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>424266; 513675</t>
+          <t>431472; 512690</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>482380; 649175</t>
+          <t>603732; 680237</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>490279; 579501</t>
+          <t>495791; 587312</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>590588; 690751</t>
+          <t>590917; 697437</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>835327; 953403</t>
+          <t>834154; 945728</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1002690; 1246614</t>
+          <t>1217370; 1340301</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales (tasa de respuesta: 100,0%)</t>
+          <t>Población que conforma un hogar unipersonal (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
